--- a/parameters/UA/hydrogen/transport_parameters.xlsx
+++ b/parameters/UA/hydrogen/transport_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samiyhanaqvi/Desktop/na/hydrogen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2859\Desktop\Geo-X\Geo-X\parameters\UA\hydrogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA04D262-52CD-E84A-AACA-090BBB08E1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83631402-C317-461F-B68C-DF4B69E02E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17240" xr2:uid="{01CAD706-003C-4A74-9F03-CC297AE4FC2E}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{01CAD706-003C-4A74-9F03-CC297AE4FC2E}"/>
   </bookViews>
   <sheets>
     <sheet name="500 bar" sheetId="1" r:id="rId1"/>
@@ -439,17 +439,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23198DE7-106D-4D74-B711-F3D7F49409F2}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -457,7 +457,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -465,7 +465,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -473,15 +473,15 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -489,7 +489,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -497,7 +497,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -505,7 +505,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -513,7 +513,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -521,7 +521,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -529,7 +529,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -537,7 +537,7 @@
         <v>660000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -545,7 +545,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -553,7 +553,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -561,7 +561,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -577,17 +577,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{875274DB-A5D7-44A9-AC4D-2201EE76E33C}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -595,7 +595,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -603,7 +603,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -611,15 +611,15 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -627,7 +627,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -635,7 +635,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -643,7 +643,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -651,7 +651,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -659,7 +659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -667,7 +667,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -675,7 +675,7 @@
         <v>860000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -691,7 +691,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -699,7 +699,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -715,17 +715,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4B59BD7-1EF7-434C-B129-C023F2EA056C}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -733,7 +733,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -741,7 +741,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -749,15 +749,15 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -765,7 +765,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -773,7 +773,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -781,7 +781,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -789,7 +789,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -797,7 +797,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -805,7 +805,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -813,7 +813,7 @@
         <v>660000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -821,7 +821,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -829,7 +829,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -837,7 +837,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -853,17 +853,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2336249F-38D8-48A5-AB33-F1F0C167058D}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -871,7 +871,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -879,7 +879,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -887,15 +887,15 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -903,7 +903,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -911,7 +911,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -919,7 +919,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -927,7 +927,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -935,7 +935,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -943,7 +943,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -951,7 +951,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -959,7 +959,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -967,7 +967,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -975,7 +975,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
